--- a/Matriz de Trazabilidad.xlsx
+++ b/Matriz de Trazabilidad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emacr\Desktop\Entrega 6 Trimestre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emacr\Desktop\Proyecto\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDB6098-EB5A-4F5E-BBD7-801B957BA605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE57460B-4A39-4D97-AA78-50E5A8B0CD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -234,27 +234,6 @@
     <t>Info 7: Datos usuario, vehículo, historial reservas</t>
   </si>
   <si>
-    <t>RF-08</t>
-  </si>
-  <si>
-    <t>Guardar estacionamientos favoritos</t>
-  </si>
-  <si>
-    <t>Los usuarios deben poder marcar hasta 10 estacionamientos como favoritos, accesibles desde perfil</t>
-  </si>
-  <si>
-    <t>Favoritos reducen tiempo de búsqueda recurrente en 70% para usuarios frecuentes</t>
-  </si>
-  <si>
-    <t>Agilizar acceso a lugares frecuentes</t>
-  </si>
-  <si>
-    <t>R.1.8</t>
-  </si>
-  <si>
-    <t>Info 8: Lista hasta 10 estacionamientos favoritos</t>
-  </si>
-  <si>
     <t>RESERVAS</t>
   </si>
   <si>
@@ -345,102 +324,12 @@
     <t>Info 12: Política cancelación y tiempo límite</t>
   </si>
   <si>
-    <t>PAGOS</t>
-  </si>
-  <si>
-    <t>RF-13</t>
-  </si>
-  <si>
-    <t>Pago</t>
-  </si>
-  <si>
-    <t>Métodos de pago seguros</t>
-  </si>
-  <si>
-    <t>El sistema debe soportar mínimo 3 métodos (tarjetas crédito/débito, billetera digital), encriptados según PCI DSS</t>
-  </si>
-  <si>
-    <t>Múltiples métodos de pago aumentan tasa de conversión en 35% y generan confianza</t>
-  </si>
-  <si>
-    <t>Facilitar transacciones seguras y convenientes</t>
-  </si>
-  <si>
-    <t>R.1.13</t>
-  </si>
-  <si>
-    <t>Info 13: Métodos pago con encriptación PCI DSS</t>
-  </si>
-  <si>
-    <t>RF-14</t>
-  </si>
-  <si>
-    <t>Calcular costo de estacionamiento</t>
-  </si>
-  <si>
-    <t>El sistema debe calcular automáticamente costo según duración y tarifas (hora/día/semana), aplicando descuentos disponibles</t>
-  </si>
-  <si>
-    <t>Cálculo automático elimina errores en 100% y transparenta costos al usuario</t>
-  </si>
-  <si>
-    <t>Determinar precio justo y transparente</t>
-  </si>
-  <si>
-    <t>R.1.14</t>
-  </si>
-  <si>
-    <t>Info 14: Tarifas por duración y descuentos</t>
-  </si>
-  <si>
-    <t>RF-15</t>
-  </si>
-  <si>
-    <t>Generar recibos</t>
-  </si>
-  <si>
-    <t>Tras cada pago exitoso generar recibo PDF detallado, enviado por email y disponible en app por 12 meses</t>
-  </si>
-  <si>
-    <t>Recibos digitales facilitan contabilidad y reducen consultas de comprobantes en 80%</t>
-  </si>
-  <si>
-    <t>Proporcionar comprobante para registros contables</t>
-  </si>
-  <si>
-    <t>R.1.15</t>
-  </si>
-  <si>
-    <t>Info 15: Recibo PDF disponible 12 meses</t>
-  </si>
-  <si>
     <t>NOTIFICACIONES</t>
   </si>
   <si>
-    <t>RF-16</t>
-  </si>
-  <si>
     <t>Notificación</t>
   </si>
   <si>
-    <t>Recordatorios de reserva</t>
-  </si>
-  <si>
-    <t>El sistema debe enviar recordatorios 2 horas y 30 minutos antes de llegada por push y opcionalmente SMS</t>
-  </si>
-  <si>
-    <t>Recordatorios reducen no-shows en 45% y optimizan uso de espacios</t>
-  </si>
-  <si>
-    <t>Reducir ausencias y maximizar ocupación</t>
-  </si>
-  <si>
-    <t>R.1.16</t>
-  </si>
-  <si>
-    <t>Info 16: Recordatorios push/SMS programados</t>
-  </si>
-  <si>
     <t>RF-17</t>
   </si>
   <si>
@@ -462,27 +351,6 @@
     <t>Info 17: Notificaciones cambios con alternativas</t>
   </si>
   <si>
-    <t>RF-18</t>
-  </si>
-  <si>
-    <t>Tiempo restante de reserva</t>
-  </si>
-  <si>
-    <t>Enviar notificación con 30 y 10 minutos restantes, ofreciendo extensión si hay disponibilidad</t>
-  </si>
-  <si>
-    <t>Alertas de tiempo evitan multas por exceso y generan ingresos adicionales por extensiones</t>
-  </si>
-  <si>
-    <t>Optimizar uso de tiempo y generar extensiones</t>
-  </si>
-  <si>
-    <t>R.1.18</t>
-  </si>
-  <si>
-    <t>Info 18: Tiempo restante con opción extensión</t>
-  </si>
-  <si>
     <t>ADMINISTRACIÓN (PROPIETARIOS)</t>
   </si>
   <si>
@@ -529,27 +397,6 @@
   </si>
   <si>
     <t>Info 20: Panel control reservas con modificación</t>
-  </si>
-  <si>
-    <t>RF-21</t>
-  </si>
-  <si>
-    <t>Establecer tarifas</t>
-  </si>
-  <si>
-    <t>Propietarios deben establecer/modificar tarifas por período (hora/día/semana) y tipo vehículo, con gracia de 24h</t>
-  </si>
-  <si>
-    <t>Flexibilidad tarifaria permite estrategias de pricing y adaptación a demanda</t>
-  </si>
-  <si>
-    <t>Permitir gestión flexible de precios</t>
-  </si>
-  <si>
-    <t>R.1.21</t>
-  </si>
-  <si>
-    <t>Info 21: Tarifas por período con gracia 24h</t>
   </si>
   <si>
     <t>RF-22</t>
@@ -1254,17 +1101,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1282,18 +1141,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1576,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -1624,20 +1471,20 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:10" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="11"/>
+    </row>
+    <row r="3" spans="1:10" ht="189.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1669,7 +1516,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="174" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -1701,7 +1548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="174" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -1733,7 +1580,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1765,7 +1612,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="252.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
@@ -1830,18 +1677,18 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="16"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:10" ht="189.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -1875,61 +1722,61 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:10" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="I12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:10" ht="174" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>78</v>
@@ -1938,7 +1785,7 @@
         <v>79</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>80</v>
@@ -1953,7 +1800,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="268.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>84</v>
       </c>
@@ -1961,7 +1808,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>85</v>
@@ -1970,7 +1817,7 @@
         <v>86</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>87</v>
@@ -1985,7 +1832,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="252.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>91</v>
       </c>
@@ -1993,7 +1840,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>92</v>
@@ -2002,7 +1849,7 @@
         <v>93</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>94</v>
@@ -2017,1246 +1864,1010 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:10" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+      <c r="I17" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="18" spans="1:10" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="1:10" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:10" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="I21" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="2" t="s">
+    </row>
+    <row r="24" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="237" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="237" thickBot="1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="284.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>7</v>
+        <v>149</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="30" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="J30" s="13"/>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="J33" s="13"/>
     </row>
     <row r="34" spans="1:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="17"/>
-    </row>
-    <row r="35" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="J35" s="9"/>
+        <v>175</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="J36" s="9"/>
-    </row>
-    <row r="37" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" spans="1:10" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="J37" s="9"/>
-    </row>
-    <row r="38" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="J38" s="9"/>
+        <v>193</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" spans="1:10" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="17"/>
-    </row>
-    <row r="40" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" ht="189.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="J40" s="9"/>
+        <v>201</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="J40" s="13"/>
     </row>
     <row r="41" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="J41" s="9"/>
+        <v>207</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="J41" s="13"/>
     </row>
     <row r="42" spans="1:10" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="17"/>
-    </row>
-    <row r="43" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="J43" s="9"/>
+        <v>214</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="J43" s="13"/>
     </row>
     <row r="44" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="I46" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:10" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="B47" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="1:10" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="J44" s="9"/>
-    </row>
-    <row r="45" spans="1:10" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="J45" s="9"/>
-    </row>
-    <row r="46" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="G50" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="J46" s="9"/>
-    </row>
-    <row r="47" spans="1:10" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="17"/>
-    </row>
-    <row r="48" spans="1:10" ht="189.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="E51" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="H48" s="7" t="s">
+      <c r="G51" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="H51" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="J48" s="9"/>
-    </row>
-    <row r="49" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="I51" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="B53" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="I49" s="8" t="s">
+      <c r="G53" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="J49" s="9"/>
-    </row>
-    <row r="50" spans="1:10" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
+      <c r="H53" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="17"/>
-    </row>
-    <row r="51" spans="1:10" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+      <c r="I53" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="J51" s="9"/>
-    </row>
-    <row r="52" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="J52" s="9"/>
-    </row>
-    <row r="53" spans="1:10" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="17"/>
+      <c r="J53" s="13"/>
     </row>
     <row r="54" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="F54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="J54" s="9"/>
-    </row>
-    <row r="55" spans="1:10" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G55" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="J55" s="9"/>
-    </row>
-    <row r="56" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="J56" s="9"/>
-    </row>
-    <row r="57" spans="1:10" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="17"/>
-    </row>
-    <row r="58" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="J58" s="9"/>
-    </row>
-    <row r="59" spans="1:10" ht="111" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="J59" s="9"/>
-    </row>
-    <row r="60" spans="1:10" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="17"/>
-    </row>
-    <row r="61" spans="1:10" ht="174" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="J61" s="9"/>
-    </row>
-    <row r="62" spans="1:10" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="I62" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="J62" s="9"/>
-    </row>
-    <row r="63" spans="1:10" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="J63" s="11"/>
-    </row>
+        <v>272</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="J55" s="15"/>
+    </row>
+    <row r="57" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:10" ht="174" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A39:J39"/>
+  <mergeCells count="36">
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I53:J53"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="I55:J55"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I47:J47"/>
     <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A9:J9"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="I41:J41"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A42:J42"/>
+    <mergeCell ref="I33:J33"/>
     <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I33:J33"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="I27:J27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
